--- a/naver-place-crawler/results_nail/서귀포시_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/서귀포시_네일샵.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -564,12 +564,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>란나네일</t>
+          <t>버디네일</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>araearae@naver.com</t>
+          <t>hhj6910@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -577,12 +577,12 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 중문상로 41-3</t>
+          <t>제주특별자치도 서귀포시 법환상로 20 F동 102호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/__buddy.nail</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -613,17 +613,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>170</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>5</v>
+        <v>174</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -632,17 +632,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1315968519</t>
+          <t>1805642729</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1315968519</t>
+          <t>https://m.place.naver.com/place/1805642729</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -654,25 +654,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>네일더하기</t>
+          <t>네일올레</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>doyi2@naver.com</t>
+          <t>cptp6195@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0507-1317-1726</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 천제연로207번길 7 더프라임시티 1층</t>
+          <t>제주특별자치도 서귀포시 중앙로 69 109호 네일올레</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_plus_jm</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -682,7 +686,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -703,17 +707,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -722,17 +726,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1826992246</t>
+          <t>1737644438</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1826992246</t>
+          <t>https://m.place.naver.com/place/1737644438</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -744,29 +748,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>네일마커</t>
+          <t>네일더이쁨</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>reform6752@naver.com</t>
+          <t>pbr8084@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>064-783-1012</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 성산읍 고성동서로56번길 10-1 1층</t>
+          <t>제주특별자치도 서귀포시 대정읍 상모로289번길 16-7 1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_marker</t>
+          <t>https://www.instagram.com/nail_the_ibbum</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -816,17 +816,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1348294347</t>
+          <t>1766718466</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1348294347</t>
+          <t>https://m.place.naver.com/place/1766718466</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -838,39 +838,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일금비</t>
+          <t>구억리네일쌀롱</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mneilacademy@naver.com</t>
+          <t>kohy510@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1456-0184</t>
+          <t>0507-1312-9909</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 솔동산로22번길 18-4 1층</t>
+          <t>제주특별자치도 서귀포시 대정읍 영어도시로 9 제주에듀골드힐 101동 1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_ppxlxaG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -886,22 +886,22 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -910,17 +910,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1421848631</t>
+          <t>1727513445</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1421848631</t>
+          <t>https://m.place.naver.com/place/1727513445</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -932,29 +932,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>네요네일</t>
+          <t>더네일온</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>keto_merry@naver.com</t>
+          <t>jiyeon6305@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1492-2898</t>
+          <t>0507-1426-3710</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 태평로449번길 13 1층</t>
+          <t>제주특별자치도 서귀포시 대정읍 글로벌에듀로 370 148호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/neyo.nail</t>
+          <t>https://www.instagram.com/the_nail_on?igsh=OWV6c2NvcTc4b3R0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -989,13 +989,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1004,17 +1004,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2057647535</t>
+          <t>1865273760</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2057647535</t>
+          <t>https://m.place.naver.com/place/1865273760</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1026,29 +1026,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>빈네일스튜디오</t>
+          <t>네일스튜디오 리에토</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>whoabc@naver.com</t>
+          <t>enoch_mwon@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1311-7131</t>
+          <t>0507-1398-1508</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 표선면 번영로3428번길 129 상가동 102호(gs편의점 옆)</t>
+          <t>제주특별자치도 서귀포시 동홍중앙로90번길 4-8 네일스튜디오 리에토</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bin_nail.studio</t>
+          <t>https://www.instagram.com/nailstudio_lieto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1083,13 +1083,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="Q7" t="n">
         <v>9</v>
       </c>
       <c r="R7" t="n">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1148723821</t>
+          <t>1127541291</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1148723821</t>
+          <t>https://m.place.naver.com/place/1127541291</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1120,29 +1120,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>네일더끌림</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>rlduswlsl84@naver.com</t>
-        </is>
-      </c>
+          <t>은미네일</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1374-0558</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 천지로 20 2층</t>
+          <t>제주특별자치도 서귀포시 성산읍 동류암로36번길 22-1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://instagram.com/___.cclim</t>
+          <t>http://instagram.com/eunminail</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1177,13 +1169,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,17 +1184,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1315971497</t>
+          <t>35816192</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1315971497</t>
+          <t>https://m.place.naver.com/place/35816192</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1214,34 +1206,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>네일은봄날</t>
+          <t>미네일</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bomnal6878@naver.com</t>
+          <t>onelovekmh@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>064-792-7456</t>
+          <t>064-732-4199</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 대정읍 동일하모로 195-2 1층</t>
+          <t>제주특별자치도 서귀포시 동홍남로 73 1층 미네일</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://mtsolution.co.kr/nailthe</t>
+          <t>https://www.instagram.com/minail7324199</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1267,17 +1259,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="Q9" t="n">
-        <v>9</v>
-      </c>
       <c r="R9" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,17 +1278,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1915180087</t>
+          <t>37852718</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1915180087</t>
+          <t>https://m.place.naver.com/place/37852718</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1308,24 +1300,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>네일사랑</t>
+          <t>비비네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>longlonghaha@naver.com</t>
+          <t>milkycoco95@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>064-733-3729</t>
+          <t>064-732-0365</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 태평로 533</t>
+          <t>제주특별자치도 서귀포시 중정로 45</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1365,13 +1357,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,17 +1372,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>932202247</t>
+          <t>30855716</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/932202247</t>
+          <t>https://m.place.naver.com/place/30855716</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1402,29 +1394,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>칸나네일</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>choej88a@naver.com</t>
-        </is>
-      </c>
+          <t>살롱멜로</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1378-8650</t>
+          <t>0507-1470-0778</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 동홍서로112번길 19 1층</t>
+          <t>제주특별자치도 서귀포시 신북로 27 1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cannanail_/</t>
+          <t>http://instagram.com/melo_nail_sui</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1459,13 +1447,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="R11" t="n">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,17 +1462,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2094254153</t>
+          <t>1190639964</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2094254153</t>
+          <t>https://m.place.naver.com/place/1190639964</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1496,29 +1484,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>닥터아이티엔 강남스킨케어</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>fabrunch@naver.com</t>
-        </is>
-      </c>
+          <t>네일마커</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1398-8829</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 태평로431번길 3 디아일랜드블루호텔1층 102호</t>
+          <t>제주특별자치도 서귀포시 성산읍 고성동서로56번길 10-1</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kangnambeauty_jeju</t>
+          <t>https://www.instagram.com/nail_marker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1553,13 +1533,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>103</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>186</v>
+        <v>3</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,17 +1548,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>21018516</t>
+          <t>1224022839</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21018516</t>
+          <t>https://m.place.naver.com/place/1224022839</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1590,29 +1570,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>요이네일</t>
+          <t>닥터아이티엔 강남스킨케어</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>a_bbbbb@naver.com</t>
+          <t>fabrunch@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1312-9744</t>
+          <t>0507-1398-8829</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 신서귀로 43 203호</t>
+          <t>제주특별자치도 서귀포시 태평로431번길 3 디아일랜드블루호텔1층 102호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yoi.nail_</t>
+          <t>https://www.instagram.com/kangnambeauty_jeju</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1638,7 +1618,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1647,13 +1627,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>83</v>
       </c>
       <c r="R13" t="n">
-        <v>15</v>
+        <v>186</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1662,17 +1642,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2071583094</t>
+          <t>21018516</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2071583094</t>
+          <t>https://m.place.naver.com/place/21018516</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1684,29 +1664,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>오드리샵</t>
+          <t>피어나</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>skinbeauty7@naver.com</t>
+          <t>sksql0318@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1398-7325</t>
+          <t>0507-1326-5205</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 성산읍 산성효자로 11-7 퍼스트빌C 1층오드리샵</t>
+          <t>제주특별자치도 서귀포시 동홍동로 37 1층 피어나</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/audreyshop_00</t>
+          <t>https://blog.naver.com/sksql0318</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1721,7 +1701,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1741,13 +1721,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="R14" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1756,17 +1736,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1685197213</t>
+          <t>38328592</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1685197213</t>
+          <t>https://m.place.naver.com/place/38328592</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1778,25 +1758,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>탑네일</t>
+          <t>빈네일스튜디오</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>eunoia737@naver.com</t>
+          <t>whoabc@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1311-7131</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 남원읍 남조로 5 1층</t>
+          <t>제주특별자치도 서귀포시 표선면 번영로3428번길 129 상가동 102호(gs편의점 옆)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/bin_nail.studio</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1806,7 +1790,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1827,17 +1811,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>43</v>
+        <v>107</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R15" t="n">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1846,17 +1830,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1273092905</t>
+          <t>1148723821</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1273092905</t>
+          <t>https://m.place.naver.com/place/1148723821</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1852,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>네일효</t>
+          <t>미녀공장하모니</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mellenging@naver.com</t>
+          <t>monobono00@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1881,22 +1865,22 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 대정읍 동일하모로 204 1층</t>
+          <t>제주특별자치도 서귀포시 동홍남로 83 1층 미녀공장하모니</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_kSvcb</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1912,22 +1896,22 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1936,17 +1920,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1692005380</t>
+          <t>1361052531</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1692005380</t>
+          <t>https://m.place.naver.com/place/1361052531</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1958,29 +1942,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>누크뷰티</t>
+          <t>네일마커</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>likesosomi@naver.com</t>
+          <t>reform6752@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1311-4539</t>
+          <t>064-783-1012</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 이어도로 936-1 2층</t>
+          <t>제주특별자치도 서귀포시 성산읍 고성동서로56번길 10-1 1층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/noo.k__?igsh=MXI2OGo5dWV2MDAybA%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/nail_marker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2015,13 +1999,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2030,17 +2014,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2028979126</t>
+          <t>1348294347</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2028979126</t>
+          <t>https://m.place.naver.com/place/1348294347</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2052,29 +2036,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>네일바다 닥터풋클린 본점</t>
+          <t>미미네일</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>tjsgmlzoq92@naver.com</t>
+          <t>kensgirl1206@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1396-4182</t>
+          <t>0507-1478-7535</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 대청로25번길 6-9 상가동 1층 102호 네일바다닥터풋클린</t>
+          <t>제주특별자치도 서귀포시 일주동로 8556 2층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_bada_amanda</t>
+          <t>http://instagram.com/miminail7942</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2109,13 +2093,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>473</v>
+        <v>5</v>
       </c>
       <c r="Q18" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>596</v>
+        <v>5</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2124,17 +2108,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1056365302</t>
+          <t>1684793911</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1056365302</t>
+          <t>https://m.place.naver.com/place/1684793911</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2146,30 +2130,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>버디네일</t>
+          <t>네일은봄날</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>hhj6910@naver.com</t>
+          <t>bomnal6878@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>064-792-7456</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 법환상로 20 F동 102호</t>
+          <t>제주특별자치도 서귀포시 대정읍 동일하모로 195-2 1층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/__buddy.nail</t>
+          <t>http://mtsolution.co.kr/nailthe</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2195,17 +2183,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="R19" t="n">
-        <v>174</v>
+        <v>10</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2214,17 +2202,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1805642729</t>
+          <t>1915180087</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1805642729</t>
+          <t>https://m.place.naver.com/place/1915180087</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2236,34 +2224,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>바른네일</t>
+          <t>몽글네일</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>fforever1130@naver.com</t>
+          <t>0_0kmg@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1485-1277</t>
+          <t>0507-1445-5698</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 신동로67번길 13 B동 101호</t>
+          <t>제주특별자치도 서귀포시 중산간동로 7999 1층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bareun_nail_</t>
+          <t>http://pf.kakao.com/_axhJbn</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2284,7 +2272,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2293,13 +2281,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2308,17 +2296,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1511574554</t>
+          <t>1123802903</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1511574554</t>
+          <t>https://m.place.naver.com/place/1123802903</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2330,12 +2318,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>탑클래스네일&amp;브로우</t>
+          <t>란나네일</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>vlvivi@naver.com</t>
+          <t>araearae@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -2343,7 +2331,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 대정읍 에듀시티로 48 1층</t>
+          <t>제주특별자치도 서귀포시 중문상로 41-3</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2383,13 +2371,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>97</v>
+        <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>98</v>
+        <v>5</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2398,17 +2386,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1107592307</t>
+          <t>1315968519</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1107592307</t>
+          <t>https://m.place.naver.com/place/1315968519</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2420,29 +2408,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>이트네일</t>
+          <t>네일드초이</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>kjw9909ing@naver.com</t>
+          <t>tkatns289@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0507-1472-5962</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 안덕면 산방로 3 1층 이트네일 스튜디오</t>
+          <t>제주특별자치도 서귀포시 서호남로32번길 10-2 1층 건앤로빈스 안</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yeet_nail</t>
+          <t>https://www.instagram.com/nail_de_choi?igsh=MXVlMTZkdm5henc2Zw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2477,13 +2461,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>124</v>
+        <v>219</v>
       </c>
       <c r="Q22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2492,17 +2476,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1772939138</t>
+          <t>1823333907</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1772939138</t>
+          <t>https://m.place.naver.com/place/1823333907</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2514,25 +2498,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>네일또만나</t>
+          <t>네요네일</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ehgptn321@naver.com</t>
+          <t>keto_merry@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1492-2898</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 동홍남로 81 1층 네일또만나</t>
+          <t>제주특별자치도 서귀포시 태평로449번길 13 1층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail.ddomanna</t>
+          <t>https://www.instagram.com/neyo.nail</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2558,7 +2546,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2567,13 +2555,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2582,17 +2570,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1951868768</t>
+          <t>2057647535</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1951868768</t>
+          <t>https://m.place.naver.com/place/2057647535</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2604,29 +2592,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>아라네일</t>
+          <t>네일효</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>trueprecious@naver.com</t>
+          <t>mellenging@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0507-1456-1407</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 표선면 표선동서로 246 1층</t>
+          <t>제주특별자치도 서귀포시 대정읍 동일하모로 204 1층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_vxiyFn/chat</t>
+          <t>http://pf.kakao.com/_kSvcb</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2661,13 +2645,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R24" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2676,17 +2660,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2010066546</t>
+          <t>1692005380</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2010066546</t>
+          <t>https://m.place.naver.com/place/1692005380</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2698,29 +2682,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>네일또만나요 성산점</t>
+          <t>요이네일</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>okgirl27@naver.com</t>
+          <t>a_bbbbb@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1378-0969</t>
+          <t>0507-1312-9744</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 성산읍 고성오조로 90</t>
+          <t>제주특별자치도 서귀포시 신서귀로 43 203호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/yoi.nail_</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2730,7 +2714,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2746,22 +2730,22 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2770,17 +2754,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1140027847</t>
+          <t>2071583094</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1140027847</t>
+          <t>https://m.place.naver.com/place/2071583094</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2792,35 +2776,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>민아뷰티샵</t>
+          <t>더나은네일</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sanso267@naver.com</t>
+          <t>merryyear09@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1362-1541</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 표선면 표선중앙로 93 1층</t>
+          <t>제주특별자치도 서귀포시 대정읍 하모중앙로 69 더나은네일</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_YfCpxb</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2836,22 +2824,22 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2860,17 +2848,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1779957700</t>
+          <t>1262567469</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1779957700</t>
+          <t>https://m.place.naver.com/place/1262567469</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2882,29 +2870,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>루다네일</t>
+          <t>소네네일</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>gmlehd_96@naver.com</t>
+          <t>ljh6971@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>064-762-6750</t>
+          <t>0507-1391-6260</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 홍중로 23</t>
+          <t>제주특별자치도 서귀포시 신동로27번길 17 1층 소네네일(SONE NAIL)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/sonenail_23</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2914,7 +2902,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2935,17 +2923,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>4</v>
+        <v>169</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>4</v>
+        <v>171</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2954,17 +2942,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>38410716</t>
+          <t>1154302277</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38410716</t>
+          <t>https://m.place.naver.com/place/1154302277</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2976,12 +2964,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>네일바이민</t>
+          <t>민아뷰티샵</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>tweety87524@naver.com</t>
+          <t>sanso267@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2989,12 +2977,12 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 선반로 37 2층</t>
+          <t>제주특별자치도 서귀포시 표선면 표선중앙로 93 1층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>http://instagram.com/nailbymin_minah</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3004,7 +2992,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3025,17 +3013,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3044,17 +3032,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1243890667</t>
+          <t>1779957700</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1243890667</t>
+          <t>https://m.place.naver.com/place/1779957700</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3066,29 +3054,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>비비네일</t>
+          <t>인생네일</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>milkycoco95@naver.com</t>
+          <t>kimcoolove@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>064-732-0365</t>
+          <t>0507-1336-3319</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 중정로 45</t>
+          <t>제주특별자치도 서귀포시 신서로32번길 10 베스킨라빈스 옆</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/artist_lavie</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3098,7 +3086,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3119,17 +3107,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R29" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3138,17 +3126,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>30855716</t>
+          <t>1712515646</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/30855716</t>
+          <t>https://m.place.naver.com/place/1712515646</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3160,29 +3148,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>미미네일</t>
+          <t>네일더맑음</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>kensgirl1206@naver.com</t>
+          <t>pphy1027@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1478-7535</t>
+          <t>0507-1337-7332</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 일주동로 8556 2층</t>
+          <t>제주특별자치도 서귀포시 동문로 16 1층 네일더맑음</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>http://instagram.com/miminail7942</t>
+          <t>http://www.instagram.com/nailthe_sunny</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3217,13 +3205,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3232,17 +3220,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1684793911</t>
+          <t>1431700125</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1684793911</t>
+          <t>https://m.place.naver.com/place/1431700125</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3254,39 +3242,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>시안네일</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>design_by_d2m@naver.com</t>
-        </is>
-      </c>
+          <t>네일드결</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1377-4145</t>
+          <t>0507-1364-2640</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 성산읍 일주동로 4280 2층</t>
+          <t>제주특별자치도 서귀포시 서호중로 84 2층 살롱드결</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_xmvcLxj</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3302,22 +3286,22 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3326,17 +3310,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1977611689</t>
+          <t>1489091200</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1977611689</t>
+          <t>https://m.place.naver.com/place/1489091200</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3348,29 +3332,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>솜솜네일</t>
+          <t>오늘네일</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>mydbfla33@naver.com</t>
+          <t>webmaia21@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>0507-1462-0620</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 중정로 19-6 1층</t>
+          <t>제주특별자치도 서귀포시 동홍동로 27 102호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/som.som_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3380,7 +3360,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3401,17 +3381,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3420,17 +3400,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1620869487</t>
+          <t>1294082748</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1620869487</t>
+          <t>https://m.place.naver.com/place/1294082748</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3442,29 +3422,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>네일스토리</t>
+          <t>미깡네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>grayhall@naver.com</t>
+          <t>ch___bg@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0507-1325-0251</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 중정로 76-1 2층</t>
+          <t>제주특별자치도 서귀포시 일주동로 8702 1층 102호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/grayhall</t>
+          <t>https://www.instagram.com/mikkang_nail</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3479,7 +3455,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3495,17 +3471,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="Q33" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="R33" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3514,17 +3490,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>37879281</t>
+          <t>1642225158</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37879281</t>
+          <t>https://m.place.naver.com/place/1642225158</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3536,29 +3512,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>모나네일</t>
+          <t>네일예쁜날 페디베네 제주남원점</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>brushlounge@naver.com</t>
+          <t>sugar2351@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1381-2793</t>
+          <t>0507-1321-2351</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 동홍서로112번길 7 1층</t>
+          <t>제주특별자치도 서귀포시 남원읍 태위로 673 2층 네일예쁜날</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mo.na_nail</t>
+          <t>https://www.instagram.com/nailyeppunnal/</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3593,13 +3569,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="R34" t="n">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3608,17 +3584,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1873795522</t>
+          <t>1589870132</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1873795522</t>
+          <t>https://m.place.naver.com/place/1589870132</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3630,29 +3606,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>네일팔레트</t>
+          <t>네일스토리</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>nail4season@naver.com</t>
+          <t>grayhall@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1316-6385</t>
+          <t>0507-1325-0251</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 대정읍 보성구억로 209</t>
+          <t>제주특별자치도 서귀포시 중정로 76-1 2층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/grayhall</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3662,12 +3638,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3687,13 +3663,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R35" t="n">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3702,17 +3678,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1096198009</t>
+          <t>37879281</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1096198009</t>
+          <t>https://m.place.naver.com/place/37879281</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3724,12 +3700,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>리엘르 네일</t>
+          <t>네일더하기</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>charming_0o@naver.com</t>
+          <t>doyi2@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -3737,12 +3713,12 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 표선면 표선중앙로90번길 11 리엘르네일</t>
+          <t>제주특별자치도 서귀포시 천제연로207번길 7 더프라임시티 1층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rielle_nail_cu</t>
+          <t>http://instagram.com/nail_plus_jm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3777,13 +3753,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="Q36" t="n">
         <v>2</v>
       </c>
       <c r="R36" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3792,17 +3768,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1565940748</t>
+          <t>1826992246</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1565940748</t>
+          <t>https://m.place.naver.com/place/1826992246</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3814,24 +3790,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>네일올레</t>
+          <t>여우놀이터</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>cptp6195@naver.com</t>
+          <t>jihye1980@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1317-1726</t>
+          <t>064-732-5395</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 중앙로 69 109호 네일올레</t>
+          <t>제주특별자치도 서귀포시 동문로 28-1</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3871,13 +3847,13 @@
         </is>
       </c>
       <c r="P37" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>1</v>
-      </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3886,17 +3862,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1737644438</t>
+          <t>1481422225</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1737644438</t>
+          <t>https://m.place.naver.com/place/1481422225</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3908,25 +3884,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>닥터아이티엔 서귀포점</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>뷰티인더안</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>kireina34@naver.com</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1371-0254</t>
+          <t>0507-1383-9061</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 태평로 534 1층</t>
+          <t>제주특별자치도 서귀포시 안덕면 덕수서로 159 1층 BEAUTY IN THE AN</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cbr12555/</t>
+          <t>https://www.instagram.com/beauty_inthean_nail</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3961,13 +3941,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="Q38" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3976,17 +3956,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1933689399</t>
+          <t>2018963520</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1933689399</t>
+          <t>https://m.place.naver.com/place/2018963520</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3998,25 +3978,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>네일마커</t>
+          <t>시선</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>reform6752@naver.com</t>
+          <t>emr31001@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1453-4416</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 성산읍 고성동서로56번길 10-1</t>
+          <t>제주특별자치도 서귀포시 성산읍 일주동로 4215 2층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_marker</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4026,7 +4010,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4047,17 +4031,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4066,17 +4050,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1224022839</t>
+          <t>2095355824</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1224022839</t>
+          <t>https://m.place.naver.com/place/2095355824</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4088,35 +4072,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>미녀공장하모니</t>
+          <t>아라네일</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>monobono00@naver.com</t>
+          <t>trueprecious@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1456-1407</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 동홍남로 83 1층 미녀공장하모니</t>
+          <t>제주특별자치도 서귀포시 표선면 표선동서로 246 1층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_vxiyFn/chat</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4132,22 +4120,22 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4156,17 +4144,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1361052531</t>
+          <t>2010066546</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1361052531</t>
+          <t>https://m.place.naver.com/place/2010066546</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4178,29 +4166,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>더네일온</t>
+          <t>네일러브다이브</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>jiyeon6305@naver.com</t>
+          <t>gokatchu@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1426-3710</t>
+          <t>0507-1323-3043</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 대정읍 글로벌에듀로 370 148호</t>
+          <t>제주특별자치도 서귀포시 홍중로27번길 1 1층</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/the_nail_on?igsh=OWV6c2NvcTc4b3R0</t>
+          <t>https://www.instagram.com/nail.lovedive</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4226,7 +4214,7 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4235,13 +4223,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4250,17 +4238,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1865273760</t>
+          <t>2039322421</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1865273760</t>
+          <t>https://m.place.naver.com/place/2039322421</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4272,20 +4260,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>네일그리고</t>
+          <t>네일사랑</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>noblelizent@naver.com</t>
+          <t>longlonghaha@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>064-733-3729</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 남원읍 태위로 673-2</t>
+          <t>제주특별자치도 서귀포시 태평로 533</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4325,13 +4317,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4340,17 +4332,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1119942906</t>
+          <t>932202247</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1119942906</t>
+          <t>https://m.place.naver.com/place/932202247</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4362,29 +4354,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>네일더맑음</t>
+          <t>네일펠롱</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>pphy1027@naver.com</t>
+          <t>hiel_joon@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1337-7332</t>
+          <t>0507-1326-8572</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 동문로 16 1층 네일더맑음</t>
+          <t>제주특별자치도 서귀포시 표선면 표선중앙로 106 1층2호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nailthe_sunny</t>
+          <t>https://www.instagram.com/nailpellon</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4419,13 +4411,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="Q43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4434,17 +4426,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1431700125</t>
+          <t>1619783460</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1431700125</t>
+          <t>https://m.place.naver.com/place/1619783460</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4456,20 +4448,24 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>오리엔스</t>
+          <t>시안네일</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>inter_tarot@naver.com</t>
+          <t>design_by_d2m@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1377-4145</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 남원읍 태위로 72</t>
+          <t>제주특별자치도 서귀포시 성산읍 일주동로 4280 2층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4509,13 +4505,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4524,17 +4520,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1771280157</t>
+          <t>1977611689</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1771280157</t>
+          <t>https://m.place.naver.com/place/1977611689</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4546,39 +4542,35 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>몽글네일</t>
+          <t>수네일아트</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0_0kmg@naver.com</t>
+          <t>very_cake@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0507-1445-5698</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 중산간동로 7999 1층</t>
+          <t>제주특별자치도 서귀포시 대정읍 영서중로13번길 10</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_axhJbn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4594,22 +4586,22 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4618,17 +4610,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1123802903</t>
+          <t>37578236</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1123802903</t>
+          <t>https://m.place.naver.com/place/37578236</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4640,12 +4632,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>수네일아트</t>
+          <t>린네일</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>very_cake@naver.com</t>
+          <t>sini_97@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -4653,7 +4645,7 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 대정읍 영서중로13번길 10</t>
+          <t>제주특별자치도 서귀포시 안덕면 일주서로 1479 1층 린네일</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4693,13 +4685,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4708,17 +4700,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>37578236</t>
+          <t>2031422752</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37578236</t>
+          <t>https://m.place.naver.com/place/2031422752</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4730,29 +4722,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>송네일</t>
+          <t>네일바이키키</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>jksh040404@naver.com</t>
+          <t>hyuni0324@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>064-738-3888</t>
+          <t>0507-1355-7563</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 천제연로 188 송네일</t>
+          <t>제주특별자치도 서귀포시 동홍동로 10 1층</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://instagram.com/song_nail70?utm_source=ig_profile_share&amp;igshid=79f436s5wy5</t>
+          <t>https://www.instagram.com/nail_by_kiki</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4787,13 +4779,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4802,17 +4794,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1510042589</t>
+          <t>1283062023</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1510042589</t>
+          <t>https://m.place.naver.com/place/1283062023</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4824,29 +4816,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>메이크뷰티</t>
+          <t>네일바다 닥터풋클린 본점</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>taiji0024@naver.com</t>
+          <t>tjsgmlzoq92@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1380-5997</t>
+          <t>0507-1396-4182</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 대정읍 추사로55번길 22</t>
+          <t>제주특별자치도 서귀포시 대청로25번길 6-9 상가동 1층 102호 네일바다닥터풋클린</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sJNhAkYh</t>
+          <t>https://www.instagram.com/nail_bada_amanda</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4872,7 +4864,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4881,13 +4873,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>38</v>
+        <v>473</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>123</v>
       </c>
       <c r="R48" t="n">
-        <v>39</v>
+        <v>596</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4896,17 +4888,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1108142878</t>
+          <t>1056365302</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1108142878</t>
+          <t>https://m.place.naver.com/place/1056365302</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4918,34 +4910,30 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>더나은네일</t>
+          <t>네일바이민</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>merryyear09@naver.com</t>
+          <t>tweety87524@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>0507-1362-1541</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 대정읍 하모중앙로 69 더나은네일</t>
+          <t>제주특별자치도 서귀포시 선반로 37 2층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_YfCpxb</t>
+          <t>http://instagram.com/nailbymin_minah</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4966,7 +4954,7 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4975,13 +4963,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="Q49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R49" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -4990,17 +4978,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1262567469</t>
+          <t>1243890667</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1262567469</t>
+          <t>https://m.place.naver.com/place/1243890667</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5012,29 +5000,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>시선</t>
+          <t>닥터아이티엔 서귀포점</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>emr31001@naver.com</t>
+          <t>fabrunch@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1453-4416</t>
+          <t>0507-1371-0254</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 성산읍 일주동로 4215 2층</t>
+          <t>제주특별자치도 서귀포시 태평로 534 1층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/cbr12555/</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5044,7 +5032,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5065,17 +5053,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R50" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5084,17 +5072,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>2095355824</t>
+          <t>1933689399</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2095355824</t>
+          <t>https://m.place.naver.com/place/1933689399</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5106,29 +5094,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>페디앤미 네일 서귀포본점</t>
+          <t>이네일</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>queen7373@naver.com</t>
+          <t>role_p@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1355-7249</t>
+          <t>070-4548-9461</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 일주동로 8648-3 2층</t>
+          <t>제주특별자치도 서귀포시 홍중로 25 2층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/queen7373</t>
+          <t>https://www.instagram.com/__e_nail?igsh=MW95cGN4d24xbW14ZQ==</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5143,7 +5131,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5163,13 +5151,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>101</v>
+        <v>6</v>
       </c>
       <c r="Q51" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>260</v>
+        <v>6</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5178,17 +5166,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1190652321</t>
+          <t>1552783323</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1190652321</t>
+          <t>https://m.place.naver.com/place/1552783323</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5200,29 +5188,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>토리네일</t>
+          <t>페디앤미 네일 서귀포본점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>torynail_jeju@naver.com</t>
+          <t>queen7373@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1379-5522</t>
+          <t>0507-1355-7249</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 일주동로 8572 3층 토리헤어 샵인샵</t>
+          <t>제주특별자치도 서귀포시 일주동로 8648-3 2층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/torynail_jeju</t>
+          <t>https://blog.naver.com/queen7373</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5257,13 +5245,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>162</v>
+        <v>101</v>
       </c>
       <c r="Q52" t="n">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="R52" t="n">
-        <v>311</v>
+        <v>261</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5272,17 +5260,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1380025423</t>
+          <t>1190652321</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1380025423</t>
+          <t>https://m.place.naver.com/place/1190652321</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5294,34 +5282,34 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>벨르네일</t>
+          <t>칸나네일</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>rlatpdml@naver.com</t>
+          <t>choej88a@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1419-0485</t>
+          <t>0507-1378-8650</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 홍중로 119-2 602동 1층</t>
+          <t>제주특별자치도 서귀포시 동홍서로112번길 19 1층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_AxnyeG</t>
+          <t>https://www.instagram.com/cannanail_/</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5342,7 +5330,7 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5351,13 +5339,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>432</v>
+        <v>19</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>432</v>
+        <v>19</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5366,17 +5354,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1420634838</t>
+          <t>2094254153</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1420634838</t>
+          <t>https://m.place.naver.com/place/2094254153</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5388,29 +5376,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>소중</t>
+          <t>무드 네일</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>jmst0704@naver.com</t>
+          <t>rkawkehfl211@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>064-792-7782</t>
+          <t>0507-1387-0532</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 대정읍 글로벌에듀로 390 남영에듀클래스 1층 113호</t>
+          <t>제주특별자치도 서귀포시 중문상로 72 1층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/sojungnail</t>
+          <t>https://www.instagram.com/mood.nail_</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5445,13 +5433,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="Q54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5460,17 +5448,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1896724521</t>
+          <t>1709745950</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1896724521</t>
+          <t>https://m.place.naver.com/place/1709745950</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5482,25 +5470,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>은미네일</t>
+          <t>이트네일</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>sachomi@naver.com</t>
+          <t>kjw9909ing@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1472-5962</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 성산읍 동류암로36번길 22-1</t>
+          <t>제주특별자치도 서귀포시 안덕면 산방로 3 1층 이트네일 스튜디오</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>http://instagram.com/eunminail</t>
+          <t>https://www.instagram.com/yeet_nail</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5535,13 +5527,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2</v>
+        <v>124</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R55" t="n">
-        <v>2</v>
+        <v>130</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5550,17 +5542,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>35816192</t>
+          <t>1772939138</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35816192</t>
+          <t>https://m.place.naver.com/place/1772939138</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5572,25 +5564,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>꾸밈네일</t>
+          <t>모나네일</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>smileahj@naver.com</t>
+          <t>brushlounge@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1381-2793</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 서문로29번길 1 서쪽1층 꾸밈네일</t>
+          <t>제주특별자치도 서귀포시 동홍서로112번길 7 1층</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://01084967223</t>
+          <t>https://www.instagram.com/mo.na_nail</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5621,17 +5617,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R56" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5640,17 +5636,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1015684211</t>
+          <t>1873795522</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1015684211</t>
+          <t>https://m.place.naver.com/place/1873795522</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5662,29 +5658,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>뷰티인더안</t>
+          <t>송네일</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>kireina34@naver.com</t>
+          <t>jksh040404@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1383-9061</t>
+          <t>064-738-3888</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 안덕면 덕수서로 159 1층 BEAUTY IN THE AN</t>
+          <t>제주특별자치도 서귀포시 천제연로 188 송네일</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beauty_inthean_nail</t>
+          <t>https://instagram.com/song_nail70?utm_source=ig_profile_share&amp;igshid=79f436s5wy5</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5719,13 +5715,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="Q57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5734,17 +5730,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>2018963520</t>
+          <t>1510042589</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2018963520</t>
+          <t>https://m.place.naver.com/place/1510042589</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5756,12 +5752,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>153네일_파고드는발톱.무좀발톱.물어뜯는손톱.발각질</t>
+          <t>오리엔스</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>fc5416@naver.com</t>
+          <t>inter_tarot@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -5769,12 +5765,12 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 천제연로 212-1 1층 153네일</t>
+          <t>제주특별자치도 서귀포시 남원읍 태위로 72</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fc5416</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5784,12 +5780,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5805,17 +5801,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="Q58" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5824,17 +5820,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1260273258</t>
+          <t>1771280157</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1260273258</t>
+          <t>https://m.place.naver.com/place/1771280157</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5846,25 +5842,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>네일바이키키</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>네일또만나요 성산점</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>okgirl27@naver.com</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1355-7563</t>
+          <t>0507-1378-0969</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 동홍동로 10 1층</t>
+          <t>제주특별자치도 서귀포시 성산읍 고성오조로 90</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_by_kiki</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5895,17 +5895,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R59" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5914,17 +5914,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1283062023</t>
+          <t>1140027847</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1283062023</t>
+          <t>https://m.place.naver.com/place/1140027847</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5936,25 +5936,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>네일러브다이브</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>153네일_파고드는발톱.무좀발톱.물어뜯는손톱.발각질</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>fc5416@naver.com</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>0507-1323-3043</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 홍중로27번길 1 1층</t>
+          <t>제주특별자치도 서귀포시 천제연로 212-1 1층 153네일</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.lovedive</t>
+          <t>https://blog.naver.com/fc5416</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5980,7 +5980,7 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5989,13 +5989,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R60" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6004,17 +6004,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>2039322421</t>
+          <t>1260273258</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2039322421</t>
+          <t>https://m.place.naver.com/place/1260273258</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6026,25 +6026,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>살롱멜로</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>메이크뷰티</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>taiji0024@naver.com</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1470-0778</t>
+          <t>0507-1380-5997</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 신북로 27 1층</t>
+          <t>제주특별자치도 서귀포시 대정읍 추사로55번길 22</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>http://instagram.com/melo_nail_sui</t>
+          <t>https://open.kakao.com/o/sJNhAkYh</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6070,7 +6074,7 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6079,13 +6083,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="Q61" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="R61" t="n">
-        <v>95</v>
+        <v>39</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6094,17 +6098,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1190639964</t>
+          <t>1108142878</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1190639964</t>
+          <t>https://m.place.naver.com/place/1108142878</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6120,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>네일드초이</t>
+          <t>탑클래스네일&amp;브로우</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>tkatns289@naver.com</t>
+          <t>vlvivi@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -6129,12 +6133,12 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 서호남로32번길 10-2 1층 건앤로빈스 안</t>
+          <t>제주특별자치도 서귀포시 대정읍 에듀시티로 48 1층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_de_choi?igsh=MXVlMTZkdm5henc2Zw%3D%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6144,7 +6148,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6165,17 +6169,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>219</v>
+        <v>97</v>
       </c>
       <c r="Q62" t="n">
         <v>1</v>
       </c>
       <c r="R62" t="n">
-        <v>220</v>
+        <v>98</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6184,17 +6188,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1823333907</t>
+          <t>1107592307</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1823333907</t>
+          <t>https://m.place.naver.com/place/1107592307</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6206,30 +6210,30 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>네일드결</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>리엘르 네일</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>myiworld-@naver.com</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>0507-1364-2640</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 서호중로 84 2층 살롱드결</t>
+          <t>제주특별자치도 서귀포시 표선면 표선중앙로90번길 11 리엘르네일</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xmvcLxj</t>
+          <t>https://www.instagram.com/rielle_nail_cu</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6250,7 +6254,7 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6259,13 +6263,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q63" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R63" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6274,17 +6278,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1489091200</t>
+          <t>1565940748</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1489091200</t>
+          <t>https://m.place.naver.com/place/1565940748</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6296,30 +6300,30 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>네일더이쁨</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>pbr8084@naver.com</t>
-        </is>
-      </c>
+          <t>벨르네일</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1419-0485</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 대정읍 상모로289번길 16-7 1층</t>
+          <t>제주특별자치도 서귀포시 홍중로 119-2 602동 1층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_the_ibbum</t>
+          <t>http://pf.kakao.com/_AxnyeG</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6340,7 +6344,7 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6349,13 +6353,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>432</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>432</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6364,17 +6368,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1766718466</t>
+          <t>1420634838</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1766718466</t>
+          <t>https://m.place.naver.com/place/1420634838</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6386,29 +6390,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>구억리네일쌀롱</t>
+          <t>누크뷰티</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>kohy510@naver.com</t>
+          <t>likesosomi@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1312-9909</t>
+          <t>0507-1311-4539</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 대정읍 영어도시로 9 제주에듀골드힐 101동 1층</t>
+          <t>제주특별자치도 서귀포시 이어도로 936-1 2층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/noo.k__?igsh=MXI2OGo5dWV2MDAybA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6418,7 +6422,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6439,17 +6443,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6458,17 +6462,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1727513445</t>
+          <t>2028979126</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1727513445</t>
+          <t>https://m.place.naver.com/place/2028979126</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6480,12 +6484,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>듀네일</t>
+          <t>브리에네일</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>yichury@naver.com</t>
+          <t>dajju0115@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -6493,12 +6497,12 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 동문로 48</t>
+          <t>제주특별자치도 서귀포시 동홍중앙로 55 1층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/brillernail1112</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6508,7 +6512,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6529,17 +6533,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1</v>
+        <v>339</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="R66" t="n">
-        <v>1</v>
+        <v>458</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6548,17 +6552,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>220923435</t>
+          <t>1481282228</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/220923435</t>
+          <t>https://m.place.naver.com/place/1481282228</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6570,29 +6574,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>켈리네일</t>
+          <t>네일그리고</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>kelly-art@naver.com</t>
+          <t>noblelizent@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>0507-1307-0456</t>
-        </is>
-      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 동홍중앙로 8 켈리네일</t>
+          <t>제주특별자치도 서귀포시 남원읍 태위로 673-2</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/_kellynail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6602,7 +6602,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6623,17 +6623,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>109</v>
+        <v>4</v>
       </c>
       <c r="Q67" t="n">
         <v>2</v>
       </c>
       <c r="R67" t="n">
-        <v>111</v>
+        <v>6</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6642,17 +6642,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1386951918</t>
+          <t>1119942906</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1386951918</t>
+          <t>https://m.place.naver.com/place/1119942906</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6664,29 +6664,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>피어나</t>
+          <t>탑네일</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>sksql0318@naver.com</t>
+          <t>eunoia737@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>0507-1326-5205</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 동홍동로 37 1층 피어나</t>
+          <t>제주특별자치도 서귀포시 남원읍 남조로 5 1층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sksql0318</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6696,12 +6692,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6717,17 +6713,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="Q68" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6736,17 +6732,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>38328592</t>
+          <t>1273092905</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38328592</t>
+          <t>https://m.place.naver.com/place/1273092905</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6758,25 +6754,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>미깡네일</t>
+          <t>토리네일</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ch___bg@naver.com</t>
+          <t>torynail_jeju@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1379-5522</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 일주동로 8702 1층 102호</t>
+          <t>제주특별자치도 서귀포시 일주동로 8572 3층 토리헤어 샵인샵</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mikkang_nail</t>
+          <t>https://blog.naver.com/torynail_jeju</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6811,13 +6811,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>37</v>
+        <v>162</v>
       </c>
       <c r="Q69" t="n">
-        <v>2</v>
+        <v>149</v>
       </c>
       <c r="R69" t="n">
-        <v>39</v>
+        <v>311</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6826,17 +6826,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1642225158</t>
+          <t>1380025423</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1642225158</t>
+          <t>https://m.place.naver.com/place/1380025423</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6848,34 +6848,34 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>무드 네일</t>
+          <t>원네일</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>rkawkehfl211@naver.com</t>
+          <t>soongyeolcamping@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1387-0532</t>
+          <t>0507-1476-0729</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 중문상로 72 1층</t>
+          <t>제주특별자치도 서귀포시 동홍북로 52 1층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mood.nail_</t>
+          <t>http://pf.kakao.com/_kRDzxj</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6896,7 +6896,7 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6905,13 +6905,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>35</v>
+        <v>167</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R70" t="n">
-        <v>35</v>
+        <v>171</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6920,17 +6920,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1709745950</t>
+          <t>1156771646</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1709745950</t>
+          <t>https://m.place.naver.com/place/1156771646</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6942,29 +6942,25 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>네일스튜디오 리에토</t>
+          <t>꾸밈네일</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>enoch_mwon@naver.com</t>
+          <t>smileahj@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>0507-1398-1508</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 동홍중앙로90번길 4-8 네일스튜디오 리에토</t>
+          <t>제주특별자치도 서귀포시 서문로29번길 1 서쪽1층 꾸밈네일</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailstudio_lieto</t>
+          <t>https://01084967223</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6995,17 +6991,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="Q71" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7014,17 +7010,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1127541291</t>
+          <t>1015684211</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1127541291</t>
+          <t>https://m.place.naver.com/place/1015684211</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7036,24 +7032,24 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>여우놀이터</t>
+          <t>루다네일</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>jihye1980@naver.com</t>
+          <t>gmlehd_96@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>064-732-5395</t>
+          <t>064-762-6750</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 동문로 28-1</t>
+          <t>제주특별자치도 서귀포시 홍중로 23</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7093,13 +7089,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7108,17 +7104,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1481422225</t>
+          <t>38410716</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1481422225</t>
+          <t>https://m.place.naver.com/place/38410716</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7130,25 +7126,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>브리에네일</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>dajju0115@naver.com</t>
-        </is>
-      </c>
+          <t>바른네일</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1485-1277</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 동홍중앙로 55 1층</t>
+          <t>제주특별자치도 서귀포시 신동로67번길 13 B동 101호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/brillernail1112</t>
+          <t>https://www.instagram.com/bareun_nail_</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7183,13 +7179,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>338</v>
+        <v>17</v>
       </c>
       <c r="Q73" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>457</v>
+        <v>17</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7198,17 +7194,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1481282228</t>
+          <t>1511574554</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1481282228</t>
+          <t>https://m.place.naver.com/place/1511574554</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7220,29 +7216,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>네일예쁜날 페디베네 제주남원점</t>
+          <t>네일팔레트</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>sugar2351@naver.com</t>
+          <t>nail4season@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1321-2351</t>
+          <t>0507-1316-6385</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 남원읍 태위로 673 2층 네일예쁜날</t>
+          <t>제주특별자치도 서귀포시 대정읍 보성구억로 209</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailyeppunnal/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7252,7 +7248,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7273,17 +7269,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="Q74" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7292,17 +7288,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1589870132</t>
+          <t>1096198009</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1589870132</t>
+          <t>https://m.place.naver.com/place/1096198009</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7314,34 +7310,34 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>이네일</t>
+          <t>네일금비</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>role_p@naver.com</t>
+          <t>mneilacademy@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>070-4548-9461</t>
+          <t>0507-1456-0184</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 홍중로 25 2층</t>
+          <t>제주특별자치도 서귀포시 솔동산로22번길 18-4 1층</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/__e_nail?igsh=MW95cGN4d24xbW14ZQ==</t>
+          <t>http://pf.kakao.com/_ppxlxaG</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7362,7 +7358,7 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7371,13 +7367,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7386,17 +7382,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1552783323</t>
+          <t>1421848631</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1552783323</t>
+          <t>https://m.place.naver.com/place/1421848631</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7408,25 +7404,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>린네일</t>
+          <t>켈리네일</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>sini_97@naver.com</t>
+          <t>kelly-art@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1307-0456</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 안덕면 일주서로 1479 1층 린네일</t>
+          <t>제주특별자치도 서귀포시 동홍중앙로 8 켈리네일</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/_kellynail</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7457,17 +7457,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>33</v>
+        <v>110</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R76" t="n">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7476,17 +7476,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>2031422752</t>
+          <t>1386951918</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2031422752</t>
+          <t>https://m.place.naver.com/place/1386951918</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7498,25 +7498,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>오늘네일</t>
+          <t>소중</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>barbie0903@naver.com</t>
+          <t>jmst0704@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>064-792-7782</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 동홍동로 27 102호</t>
+          <t>제주특별자치도 서귀포시 대정읍 글로벌에듀로 390 남영에듀클래스 1층 113호</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/sojungnail</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7526,7 +7530,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -7547,17 +7551,17 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P77" t="n">
         <v>6</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R77" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7566,17 +7570,17 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>1294082748</t>
+          <t>1896724521</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1294082748</t>
+          <t>https://m.place.naver.com/place/1896724521</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7588,29 +7592,25 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>네일보리</t>
+          <t>네일또만나</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>kd_43@naver.com</t>
+          <t>ehgptn321@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>0507-1440-6933</t>
-        </is>
-      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 중앙로 196 4층</t>
+          <t>제주특별자치도 서귀포시 동홍남로 81 1층 네일또만나</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nail_bori__/profilecard/?igsh=MTU4cmFqNjVtN3M2bA==</t>
+          <t>http://www.instagram.com/nail.ddomanna</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7636,7 +7636,7 @@
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -7645,13 +7645,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7660,17 +7660,17 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1563886452</t>
+          <t>1951868768</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1563886452</t>
+          <t>https://m.place.naver.com/place/1951868768</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7682,29 +7682,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>인생네일</t>
+          <t>네일보리</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>kimcoolove@naver.com</t>
+          <t>kd_43@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0507-1336-3319</t>
+          <t>0507-1440-6933</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 신서로32번길 10 베스킨라빈스 옆</t>
+          <t>제주특별자치도 서귀포시 중앙로 196 4층</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/artist_lavie</t>
+          <t>https://www.instagram.com/_nail_bori__/profilecard/?igsh=MTU4cmFqNjVtN3M2bA==</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7739,13 +7739,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="Q79" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7754,17 +7754,17 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1712515646</t>
+          <t>1563886452</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1712515646</t>
+          <t>https://m.place.naver.com/place/1563886452</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7776,39 +7776,35 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>원네일</t>
+          <t>듀네일</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ohnyoou@naver.com</t>
+          <t>yichury@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>0507-1476-0729</t>
-        </is>
-      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 동홍북로 52 1층</t>
+          <t>제주특별자치도 서귀포시 동문로 48</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_kRDzxj</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -7824,22 +7820,22 @@
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>167</v>
+        <v>1</v>
       </c>
       <c r="Q80" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>171</v>
+        <v>1</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7848,17 +7844,17 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>1156771646</t>
+          <t>220923435</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1156771646</t>
+          <t>https://m.place.naver.com/place/220923435</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7870,29 +7866,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>소네네일</t>
+          <t>오드리샵</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ljh6971@naver.com</t>
+          <t>skinbeauty7@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0507-1391-6260</t>
+          <t>0507-1398-7325</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 신동로27번길 17 1층 소네네일(SONE NAIL)</t>
+          <t>제주특별자치도 서귀포시 성산읍 산성효자로 11-7 퍼스트빌C 1층오드리샵</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sonenail_23</t>
+          <t>https://www.instagram.com/audreyshop_00</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7927,13 +7923,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>168</v>
+        <v>62</v>
       </c>
       <c r="Q81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>170</v>
+        <v>62</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -7942,17 +7938,17 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1154302277</t>
+          <t>1685197213</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1154302277</t>
+          <t>https://m.place.naver.com/place/1685197213</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7964,29 +7960,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>미네일</t>
+          <t>솜솜네일</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>onelovekmh@naver.com</t>
+          <t>mydbfla33@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>064-732-4199</t>
+          <t>0507-1462-0620</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 동홍남로 73 1층 미네일</t>
+          <t>제주특별자치도 서귀포시 중정로 19-6 1층</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/minail7324199</t>
+          <t>https://www.instagram.com/som.som_nail</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8021,13 +8017,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="Q82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8036,17 +8032,17 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>37852718</t>
+          <t>1620869487</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37852718</t>
+          <t>https://m.place.naver.com/place/1620869487</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8058,29 +8054,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>네일펠롱</t>
+          <t>네일더끌림</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>hiel_joon@naver.com</t>
+          <t>rlduswlsl84@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0507-1326-8572</t>
+          <t>0507-1374-0558</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 표선면 표선중앙로 106 1층2호</t>
+          <t>제주특별자치도 서귀포시 천지로 20 2층</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailpellon</t>
+          <t>http://instagram.com/___.cclim</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8115,13 +8111,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="Q83" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R83" t="n">
-        <v>98</v>
+        <v>14</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8130,17 +8126,17 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1619783460</t>
+          <t>1315971497</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1619783460</t>
+          <t>https://m.place.naver.com/place/1315971497</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8230,7 @@
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8303,13 +8299,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Q85" t="n">
         <v>2</v>
       </c>
       <c r="R85" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8328,7 +8324,7 @@
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
